--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T14:56:23+00:00</t>
+    <t>2025-01-06T16:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2831" uniqueCount="301">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -264,6 +264,10 @@
     <t>*</t>
   </si>
   <si>
+    <t xml:space="preserve">PerformerRequire:performer est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal {documentationOf.serviceEvent.performer.exists()}
+</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -411,6 +415,13 @@
     <t>ServiceEvent.id</t>
   </si>
   <si>
+    <t xml:space="preserve">Identifiant de l’évènement documenté :
+Obligatoire pour :
+- les prescriptions pour porter l'identifiant EPU de la prescription (et faisant office d'Order Placer Number) 
+- la demande d'acte d'imagerie pour porter l'Order Placer Number 
+- les CR d’imagerie pour porter le studyInstanceUID dans l'attribut @root uniquement (pas d'attribut @extension) et limité à 64 car. (voir DICOM Part 5 / section 9 Unique Identifiers (UIDs) et Annexe B Creating a Privately Defined Unique Identifier) </t>
+  </si>
+  <si>
     <t>ServiceEvent.code</t>
   </si>
   <si>
@@ -418,7 +429,198 @@
 </t>
   </si>
   <si>
+    <t>Code de l’évènement documenté :
+Obligatoire pour :
+- une demande d'acte d'imagerie 
+- un CR d’imagerie 
+- un CR d’examen de l’enfant 
+- un document d’expression personnelle du patient/usager 
+Pour les documents produits via les SNR : non utilisé</t>
+  </si>
+  <si>
     <t>Drawn from concept domain ActCode</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.code</t>
+  </si>
+  <si>
+    <t>Code de l’évènement :
+Pour les documents des professionnels :
+- Pour un document au format CDA R2 N3, se reporter au volet de contenus correspondant. 
+- Pour certains documents au format CDA R2 N1, la valeur est fixée (voir tableau qui suit). 
+- Dans les autres cas, utiliser une valeur issue d'une terminologie internationale (ex : CIM10 pour les actes) ou nationale (ex : CCAM pour les actes). 
+Pour les documents d’expression personnelle du patient/usager :
+- valeur fixée</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CD
+</t>
+  </si>
+  <si>
+    <t>Obligatoire pour :
+- un CR d’imagerie
+- un CR d’examen de l’enfant</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.translation.nullFlavor</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.translation.code</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.translation.codeSystem</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.translation.codeSystemName</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.translation.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.translation.displayName</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.translation.sdtcValueSet</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.translation.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.translation.originalText</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.translation.qualifier</t>
+  </si>
+  <si>
+    <t>Précise que le translation concerne :
+la modalité d'imagerie (obligatoire)
+la région anatomique (obligatoire)</t>
+  </si>
+  <si>
+    <t>ServiceEvent.code.translation.translation</t>
   </si>
   <si>
     <t>ServiceEvent.effectiveTime</t>
@@ -428,11 +630,345 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">Date/heure de début et de fin de l'évènement documenté :
+Précisée à la minute minimum avec précision du décalage par rapport au temps universel (UTC) </t>
+  </si>
+  <si>
+    <t>ServiceEvent.effectiveTime.nullFlavor</t>
+  </si>
+  <si>
+    <t>ServiceEvent.effectiveTime.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime {http://hl7.org/cda/stds/core/StructureDefinition/ts-simple}
+</t>
+  </si>
+  <si>
+    <t>A quantity specifying a point on the axis of natural time. A point in time is most often represented as a calendar expression.</t>
+  </si>
+  <si>
+    <t>TS.value</t>
+  </si>
+  <si>
+    <t>ServiceEvent.effectiveTime.operator</t>
+  </si>
+  <si>
+    <t>A code specifying whether the set component is included (union) or excluded (set-difference) from the set, or other set operations with the current set component and the set as constructed from the representation stream up to the current point.</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDASetOperator</t>
+  </si>
+  <si>
+    <t>SXCM_TS.operator</t>
+  </si>
+  <si>
+    <t>ServiceEvent.effectiveTime.low</t>
+  </si>
+  <si>
+    <t>Low Boundary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IVXB-TS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date/heure de début de l'évènement documenté </t>
+  </si>
+  <si>
+    <t>This is the low limit of the interval.</t>
+  </si>
+  <si>
+    <t>IVL_TS.low</t>
+  </si>
+  <si>
+    <t>ServiceEvent.effectiveTime.center</t>
+  </si>
+  <si>
+    <t>Central Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/TS
+</t>
+  </si>
+  <si>
+    <t>The arithmetic mean of the interval (low plus high divided by 2). The purpose of distinguishing the center as a semantic property is for conversions of intervals from and to point values.</t>
+  </si>
+  <si>
+    <t>IVL_TS.center</t>
+  </si>
+  <si>
+    <t>ServiceEvent.effectiveTime.width</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/PQ
+</t>
+  </si>
+  <si>
+    <t>The difference between high and low boundary. The purpose of distinguishing a width property is to handle all cases of incomplete information symmetrically. In any interval representation only two of the three properties high, low, and width need to be stated and the third can be derived.</t>
+  </si>
+  <si>
+    <t>IVL_TS.width</t>
+  </si>
+  <si>
+    <t>ServiceEvent.effectiveTime.high</t>
+  </si>
+  <si>
+    <t>High Boundary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date/heure de fin de l'évènement documenté </t>
+  </si>
+  <si>
+    <t>This is the high limit of the interval.</t>
+  </si>
+  <si>
+    <t>IVL_TS.high</t>
+  </si>
+  <si>
     <t>ServiceEvent.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Performer1
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Performer1 {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-performer}
 </t>
+  </si>
+  <si>
+    <t>Exécutant de l’évènement documenté :
+performer est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal. En effet, si 
+le document de santé est déposé dans un système d'information partagé alors l'élément 
+documentationOf/serviceEvent/performer/assignedEntity/representedOrganization/standardIndustryClassCode 
+alimente la métadonnée XDS practiceSettingCode obligatoire.</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.nullFlavor</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.realmCode</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.typeId</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.typeId.nullFlavor</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.typeId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.typeId.displayable</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.typeId.root</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.typeId.extension</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.templateId</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.typeCode</t>
+  </si>
+  <si>
+    <t>PRF pour performer (Exécutant)</t>
+  </si>
+  <si>
+    <t>PRF</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-xServiceEventPerformer</t>
+  </si>
+  <si>
+    <t>Performer1.typeCode</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.functionCode</t>
+  </si>
+  <si>
+    <t>Rôle fonctionnel</t>
+  </si>
+  <si>
+    <t>Performer1.functionCode</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.time</t>
+  </si>
+  <si>
+    <t>Date et heure de participation</t>
+  </si>
+  <si>
+    <t>Performer1.time</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AssignedEntity {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-assigned-entity}
+</t>
+  </si>
+  <si>
+    <t>Exécutant</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.nullFlavor</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.realmCode</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.typeId</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.typeId.nullFlavor</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.typeId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.typeId.displayable</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.typeId.root</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.typeId.extension</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.templateId</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.classCode</t>
+  </si>
+  <si>
+    <t>ASSIGNED</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-RoleClassAssignedEntity</t>
+  </si>
+  <si>
+    <t>AssignedEntity.classCode</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.id</t>
+  </si>
+  <si>
+    <t>AssignedEntity.id</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.sdtcIdentifiedBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IdentifiedBy
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.sdtcIdentifiedBy</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.code</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
+  </si>
+  <si>
+    <t>AssignedEntity.code</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.code.code</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.code.codeSystem</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.code.displayName</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.code.originalText</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.code.qualifier</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.code.translation</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.addr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AD
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.addr</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/TEL
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.telecom</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.assignedPerson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Person {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-person}
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.assignedPerson</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.representedOrganization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-organization}
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.representedOrganization</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.sdtcPatient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.sdtcPatient</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.sdtcPatient.id</t>
+  </si>
+  <si>
+    <t>AssignedEntity.sdtcPatient.id</t>
   </si>
 </sst>
 </file>
@@ -734,11 +1270,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK17"/>
+  <dimension ref="A1:AK89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.63671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.63671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="66.546875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="66.546875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
@@ -762,13 +1298,13 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.640625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="97.74609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="28.44140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.20703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -985,31 +1521,31 @@
         <v>74</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>74</v>
@@ -1021,11 +1557,11 @@
         <v>74</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1052,11 +1588,11 @@
         <v>74</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>74</v>
@@ -1074,7 +1610,7 @@
         <v>74</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
@@ -1094,10 +1630,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1120,11 +1656,11 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1175,7 +1711,7 @@
         <v>74</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
@@ -1195,10 +1731,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1221,11 +1757,11 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1276,7 +1812,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -1296,23 +1832,23 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -1324,11 +1860,11 @@
         <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1355,11 +1891,11 @@
         <v>74</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>74</v>
@@ -1377,7 +1913,7 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -1397,23 +1933,23 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
@@ -1425,11 +1961,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1480,7 +2016,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1500,23 +2036,23 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1528,11 +2064,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1583,7 +2119,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1603,17 +2139,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1631,11 +2167,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1644,7 +2180,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1686,7 +2222,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1706,17 +2242,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1734,11 +2270,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1789,7 +2325,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1809,10 +2345,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1835,11 +2371,11 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1890,7 +2426,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1910,10 +2446,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1924,7 +2460,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -1936,14 +2472,14 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
@@ -1965,11 +2501,11 @@
         <v>74</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -1987,7 +2523,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2007,10 +2543,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2021,7 +2557,7 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
@@ -2033,7 +2569,7 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -2044,7 +2580,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2062,11 +2598,11 @@
         <v>74</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2084,7 +2620,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2104,10 +2640,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2130,9 +2666,11 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L14" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2183,7 +2721,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2203,10 +2741,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2229,11 +2767,13 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="L15" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="M15" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2284,7 +2824,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2304,21 +2844,23 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>74</v>
@@ -2330,10 +2872,12 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
+      <c r="M16" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2359,13 +2903,11 @@
         <v>74</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>74</v>
@@ -2383,7 +2925,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2403,21 +2945,23 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -2429,10 +2973,14 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2482,21 +3030,7343 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L21" s="2"/>
+      <c r="M21" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L25" s="2"/>
+      <c r="M25" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK17" t="s" s="2">
+      <c r="AI25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L27" s="2"/>
+      <c r="M27" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="Y27" s="2"/>
+      <c r="Z27" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L28" s="2"/>
+      <c r="M28" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L29" s="2"/>
+      <c r="M29" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L30" s="2"/>
+      <c r="M30" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L31" s="2"/>
+      <c r="M31" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L32" s="2"/>
+      <c r="M32" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L35" s="2"/>
+      <c r="M35" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L39" s="2"/>
+      <c r="M39" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="Y39" s="2"/>
+      <c r="Z39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L40" s="2"/>
+      <c r="M40" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L41" s="2"/>
+      <c r="M41" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="Y41" s="2"/>
+      <c r="Z41" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L43" s="2"/>
+      <c r="M43" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L44" s="2"/>
+      <c r="M44" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L47" s="2"/>
+      <c r="M47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="Y47" s="2"/>
+      <c r="Z47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L48" s="2"/>
+      <c r="M48" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L49" s="2"/>
+      <c r="M49" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E50" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L50" s="2"/>
+      <c r="M50" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="Y50" s="2"/>
+      <c r="Z50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E51" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L51" s="2"/>
+      <c r="M51" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E52" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L52" s="2"/>
+      <c r="M52" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E53" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L53" s="2"/>
+      <c r="M53" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E54" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L54" s="2"/>
+      <c r="M54" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L55" s="2"/>
+      <c r="M55" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="Y56" s="2"/>
+      <c r="Z56" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E60" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L60" s="2"/>
+      <c r="M60" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="Y60" s="2"/>
+      <c r="Z60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L61" s="2"/>
+      <c r="M61" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L62" s="2"/>
+      <c r="M62" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E63" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L63" s="2"/>
+      <c r="M63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="Y63" s="2"/>
+      <c r="Z63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L64" s="2"/>
+      <c r="M64" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E65" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L65" s="2"/>
+      <c r="M65" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E66" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L66" s="2"/>
+      <c r="M66" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E67" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L67" s="2"/>
+      <c r="M67" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L68" s="2"/>
+      <c r="M68" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="Y69" s="2"/>
+      <c r="Z69" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="Y72" s="2"/>
+      <c r="Z72" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L73" s="2"/>
+      <c r="M73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="Y73" s="2"/>
+      <c r="Z73" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E74" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="F74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L74" s="2"/>
+      <c r="M74" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E75" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="F75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L75" s="2"/>
+      <c r="M75" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E76" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="F76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L76" s="2"/>
+      <c r="M76" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E77" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="F77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L77" s="2"/>
+      <c r="M77" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E78" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="F78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L78" s="2"/>
+      <c r="M78" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L79" s="2"/>
+      <c r="M79" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L80" s="2"/>
+      <c r="M80" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E81" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="F81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L81" s="2"/>
+      <c r="M81" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E82" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L82" s="2"/>
+      <c r="M82" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E83" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="F83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L83" s="2"/>
+      <c r="M83" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L84" s="2"/>
+      <c r="M84" s="2"/>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L85" s="2"/>
+      <c r="M85" s="2"/>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L86" s="2"/>
+      <c r="M86" s="2"/>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L87" s="2"/>
+      <c r="M87" s="2"/>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L88" s="2"/>
+      <c r="M88" s="2"/>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L89" s="2"/>
+      <c r="M89" s="2"/>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK89" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,8 +82,7 @@
   </si>
   <si>
     <t>ServiceEvent représente un évènement (acte, traitement, diagnostic, etc…) décrit dans le document. 
-L'occurrence de documentationOf/serviceEvent contenant les données de l’évènement documenté principal 
-doit inclure un élément effectiveTime et un élément performer renseignés, sans recours à l'attribut nullFlavor.</t>
+L'occurrence de documentationOf/serviceEvent contenant les données de l’évènement documenté principal doit inclure un élément effectiveTime et un élément performer renseignés, sans recours à l'attribut nullFlavor.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -264,7 +263,7 @@
     <t>*</t>
   </si>
   <si>
-    <t xml:space="preserve">PerformerRequire:performer est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal {documentationOf.serviceEvent.performer.exists()}
+    <t xml:space="preserve">PerformerRequire:performer est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal {performer.exists()}
 </t>
   </si>
   <si>
@@ -415,11 +414,10 @@
     <t>ServiceEvent.id</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifiant de l’évènement documenté :
-Obligatoire pour :
-- les prescriptions pour porter l'identifiant EPU de la prescription (et faisant office d'Order Placer Number) 
-- la demande d'acte d'imagerie pour porter l'Order Placer Number 
-- les CR d’imagerie pour porter le studyInstanceUID dans l'attribut @root uniquement (pas d'attribut @extension) et limité à 64 car. (voir DICOM Part 5 / section 9 Unique Identifiers (UIDs) et Annexe B Creating a Privately Defined Unique Identifier) </t>
+    <t>Identifiant de l’évènement documenté : Obligatoire pour :
+- les prescriptions pour porter l'identifiant EPU de la prescription (et faisant office d'Order Placer Number)
+- la demande d'acte d'imagerie pour porter l'Order Placer Number
+- les CR d’imagerie pour porter le studyInstanceUID dans l'attribut @root uniquement (pas d'attribut @extension) et limité à 64 car. (voir DICOM Part 5 / section 9 Unique Identifiers (UIDs) et Annexe B Creating a Privately Defined Unique Identifier)</t>
   </si>
   <si>
     <t>ServiceEvent.code</t>
@@ -429,12 +427,11 @@
 </t>
   </si>
   <si>
-    <t>Code de l’évènement documenté :
-Obligatoire pour :
-- une demande d'acte d'imagerie 
-- un CR d’imagerie 
-- un CR d’examen de l’enfant 
-- un document d’expression personnelle du patient/usager 
+    <t>Code de l’évènement documenté : Obligatoire pour :
+- une demande d'acte d'imagerie
+- un CR d’imagerie
+- un CR d’examen de l’enfant
+- un document d’expression personnelle du patient/usager
 Pour les documents produits via les SNR : non utilisé</t>
   </si>
   <si>
@@ -449,9 +446,9 @@
   <si>
     <t>Code de l’évènement :
 Pour les documents des professionnels :
-- Pour un document au format CDA R2 N3, se reporter au volet de contenus correspondant. 
-- Pour certains documents au format CDA R2 N1, la valeur est fixée (voir tableau qui suit). 
-- Dans les autres cas, utiliser une valeur issue d'une terminologie internationale (ex : CIM10 pour les actes) ou nationale (ex : CCAM pour les actes). 
+- Pour un document au format CDA R2 N3, se reporter au volet de contenus correspondant.
+- Pour certains documents au format CDA R2 N1, la valeur est fixée (voir tableau qui suit).
+- Dans les autres cas, utiliser une valeur issue d'une terminologie internationale (ex : CIM10 pour les actes) ou nationale (ex : CCAM pour les actes).
 Pour les documents d’expression personnelle du patient/usager :
 - valeur fixée</t>
   </si>
@@ -616,8 +613,8 @@
   </si>
   <si>
     <t>Précise que le translation concerne :
-la modalité d'imagerie (obligatoire)
-la région anatomique (obligatoire)</t>
+- la modalité d'imagerie (obligatoire)
+- la région anatomique (obligatoire)</t>
   </si>
   <si>
     <t>ServiceEvent.code.translation.translation</t>
@@ -630,8 +627,8 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Date/heure de début et de fin de l'évènement documenté :
-Précisée à la minute minimum avec précision du décalage par rapport au temps universel (UTC) </t>
+    <t>Date/heure de début et de fin de l'évènement documenté :
+Précisée à la minute minimum avec précision du décalage par rapport au temps universel (UTC)</t>
   </si>
   <si>
     <t>ServiceEvent.effectiveTime.nullFlavor</t>
@@ -675,7 +672,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Date/heure de début de l'évènement documenté </t>
+    <t>Date/heure de début de l'évènement documenté</t>
   </si>
   <si>
     <t>This is the low limit of the interval.</t>
@@ -722,7 +719,7 @@
     <t>High Boundary</t>
   </si>
   <si>
-    <t xml:space="preserve">Date/heure de fin de l'évènement documenté </t>
+    <t>Date/heure de fin de l'évènement documenté</t>
   </si>
   <si>
     <t>This is the high limit of the interval.</t>
@@ -738,11 +735,7 @@
 </t>
   </si>
   <si>
-    <t>Exécutant de l’évènement documenté :
-performer est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal. En effet, si 
-le document de santé est déposé dans un système d'information partagé alors l'élément 
-documentationOf/serviceEvent/performer/assignedEntity/representedOrganization/standardIndustryClassCode 
-alimente la métadonnée XDS practiceSettingCode obligatoire.</t>
+    <t>Exécutant de l’évènement documenté : performer est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal. En effet, si le document de santé est déposé dans un système d'information partagé alors l'élément documentationOf/serviceEvent/performer/assignedEntity/representedOrganization/standardIndustryClassCode alimente la métadonnée XDS practiceSettingCode obligatoire.</t>
   </si>
   <si>
     <t>ServiceEvent.performer.nullFlavor</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2831" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2992" uniqueCount="310">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -316,6 +316,10 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
   </si>
   <si>
     <t>ServiceEvent.typeId.nullFlavor</t>
@@ -854,6 +858,34 @@
   </si>
   <si>
     <t>AssignedEntity.id</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.id.nullFlavor</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.id.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.id.displayable</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.id.root</t>
+  </si>
+  <si>
+    <t>- Pour un professionnel : '1.2.250.1.71.4.2.1'
+- Pour le patient/usager : OID de l'autorité d'affectation de l'INS
+- Pour un système de structure : '1.2.250.1.71.4.2.1' 
+- Pour un SNR : OID de l'éditeur 
+- Pour le DP : '1.2.250.1.71.4.2.1'</t>
+  </si>
+  <si>
+    <t>A unique identifier that guarantees the global uniqueness of the instance identifier. The root alone may be the entire instance identifier.</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.id.extension</t>
+  </si>
+  <si>
+    <t>Valeur de l’identifiant</t>
   </si>
   <si>
     <t>ServiceEvent.performer.assignedEntity.sdtcIdentifiedBy</t>
@@ -1263,7 +1295,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK89"/>
+  <dimension ref="A1:AK94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="66.546875" customWidth="true" bestFit="true"/>
@@ -1817,7 +1849,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1825,10 +1857,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1926,17 +1958,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1954,11 +1986,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2009,7 +2041,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -2029,17 +2061,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -2057,11 +2089,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2112,7 +2144,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2132,17 +2164,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -2160,11 +2192,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2173,7 +2205,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -2215,7 +2247,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2235,17 +2267,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -2263,11 +2295,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2318,7 +2350,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2338,10 +2370,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2368,7 +2400,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2419,7 +2451,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2439,10 +2471,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2472,7 +2504,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
@@ -2498,7 +2530,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2516,7 +2548,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2536,10 +2568,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2573,7 +2605,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2595,7 +2627,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2613,7 +2645,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2633,10 +2665,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2662,7 +2694,7 @@
         <v>96</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2714,7 +2746,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2734,10 +2766,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2760,13 +2792,13 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2817,7 +2849,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2837,10 +2869,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2938,10 +2970,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2969,10 +3001,10 @@
         <v>86</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3023,7 +3055,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3043,17 +3075,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>75</v>
@@ -3071,11 +3103,11 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3126,7 +3158,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3146,17 +3178,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>80</v>
@@ -3174,11 +3206,11 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3229,7 +3261,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3249,17 +3281,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
@@ -3277,11 +3309,11 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3332,7 +3364,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3352,17 +3384,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>75</v>
@@ -3380,11 +3412,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3435,7 +3467,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3455,10 +3487,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3481,11 +3513,11 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3536,7 +3568,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3556,10 +3588,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3582,11 +3614,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3637,7 +3669,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3657,17 +3689,17 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>80</v>
@@ -3685,11 +3717,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3740,7 +3772,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3760,17 +3792,17 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>80</v>
@@ -3788,11 +3820,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3843,7 +3875,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3863,17 +3895,17 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3891,13 +3923,13 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3948,7 +3980,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3968,10 +4000,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4069,10 +4101,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4101,7 +4133,7 @@
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4152,7 +4184,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4172,17 +4204,17 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>80</v>
@@ -4200,11 +4232,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4255,7 +4287,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4275,17 +4307,17 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>80</v>
@@ -4303,11 +4335,11 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4358,7 +4390,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4378,17 +4410,17 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
@@ -4406,11 +4438,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4461,7 +4493,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4481,17 +4513,17 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4509,11 +4541,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4564,7 +4596,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4584,10 +4616,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4610,11 +4642,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4665,7 +4697,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4685,10 +4717,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4711,11 +4743,11 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4766,7 +4798,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4786,17 +4818,17 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>80</v>
@@ -4814,11 +4846,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4869,7 +4901,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4889,17 +4921,17 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>80</v>
@@ -4917,13 +4949,13 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4974,7 +5006,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4994,17 +5026,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -5022,11 +5054,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5077,7 +5109,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5097,10 +5129,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5123,10 +5155,10 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -5178,7 +5210,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5198,10 +5230,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5299,10 +5331,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5325,11 +5357,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5380,7 +5412,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5400,10 +5432,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5430,12 +5462,12 @@
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
@@ -5461,7 +5493,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>74</v>
@@ -5479,7 +5511,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5499,17 +5531,17 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>75</v>
@@ -5527,13 +5559,13 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5584,7 +5616,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5604,17 +5636,17 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5632,11 +5664,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5687,7 +5719,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5707,17 +5739,17 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5735,11 +5767,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5790,7 +5822,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5810,17 +5842,17 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -5838,13 +5870,13 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5895,7 +5927,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5915,10 +5947,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5941,10 +5973,10 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -5996,7 +6028,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6016,10 +6048,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6032,7 +6064,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>74</v>
@@ -6117,10 +6149,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6218,10 +6250,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6311,7 +6343,7 @@
         <v>74</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>74</v>
@@ -6319,10 +6351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6420,17 +6452,17 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
@@ -6448,11 +6480,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6503,7 +6535,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6523,17 +6555,17 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
@@ -6551,11 +6583,11 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6606,7 +6638,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6626,17 +6658,17 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>75</v>
@@ -6654,11 +6686,11 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6667,7 +6699,7 @@
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>74</v>
@@ -6709,7 +6741,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6729,17 +6761,17 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>75</v>
@@ -6757,11 +6789,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6812,7 +6844,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6832,10 +6864,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6862,7 +6894,7 @@
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6913,7 +6945,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6933,10 +6965,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6962,7 +6994,7 @@
         <v>86</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
@@ -6975,7 +7007,7 @@
         <v>74</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>74</v>
@@ -6994,7 +7026,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>74</v>
@@ -7012,7 +7044,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -7032,10 +7064,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7058,10 +7090,10 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
@@ -7113,7 +7145,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7133,10 +7165,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7159,10 +7191,10 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
@@ -7214,7 +7246,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7234,10 +7266,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7260,10 +7292,10 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -7315,7 +7347,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -7335,10 +7367,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7436,10 +7468,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7537,10 +7569,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7630,7 +7662,7 @@
         <v>74</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>74</v>
@@ -7638,10 +7670,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7739,17 +7771,17 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>80</v>
@@ -7767,11 +7799,11 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7822,7 +7854,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7842,17 +7874,17 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>80</v>
@@ -7870,11 +7902,11 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -7925,7 +7957,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -7945,17 +7977,17 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F66" t="s" s="2">
         <v>75</v>
@@ -7973,11 +8005,11 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -7986,7 +8018,7 @@
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>74</v>
@@ -8028,7 +8060,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8048,17 +8080,17 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>75</v>
@@ -8076,11 +8108,11 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8131,7 +8163,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8151,10 +8183,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8181,7 +8213,7 @@
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8232,7 +8264,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8252,10 +8284,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8289,7 +8321,7 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>74</v>
@@ -8311,7 +8343,7 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>74</v>
@@ -8329,7 +8361,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8349,10 +8381,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8428,7 +8460,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -8448,16 +8480,18 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E71" s="2"/>
+      <c r="E71" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
@@ -8474,10 +8508,12 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>268</v>
+        <v>86</v>
       </c>
       <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
+      <c r="M71" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -8503,13 +8539,11 @@
         <v>74</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>74</v>
@@ -8527,13 +8561,13 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>269</v>
+        <v>90</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>74</v>
@@ -8547,21 +8581,23 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E72" s="2"/>
+      <c r="E72" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>74</v>
@@ -8573,10 +8609,12 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
+      <c r="M72" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -8602,11 +8640,13 @@
         <v>74</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>271</v>
+        <v>74</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -8624,7 +8664,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8644,17 +8684,17 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>80</v>
@@ -8672,11 +8712,11 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8703,11 +8743,13 @@
         <v>74</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -8725,7 +8767,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8745,20 +8787,20 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>75</v>
@@ -8773,11 +8815,13 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L74" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="M74" t="s" s="2">
-        <v>138</v>
+        <v>273</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -8828,7 +8872,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8848,20 +8892,20 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>75</v>
@@ -8876,11 +8920,13 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L75" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="M75" t="s" s="2">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -8931,7 +8977,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -8960,14 +9006,12 @@
       <c r="D76" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E76" t="s" s="2">
-        <v>145</v>
-      </c>
+      <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>74</v>
@@ -8979,12 +9023,10 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>102</v>
+        <v>277</v>
       </c>
       <c r="L76" s="2"/>
-      <c r="M76" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="M76" s="2"/>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9034,13 +9076,13 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>147</v>
+        <v>278</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>74</v>
@@ -9054,23 +9096,21 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E77" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>74</v>
@@ -9082,12 +9122,10 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="L77" s="2"/>
-      <c r="M77" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="M77" s="2"/>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9113,13 +9151,11 @@
         <v>74</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>74</v>
+        <v>280</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>74</v>
@@ -9137,7 +9173,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>151</v>
+        <v>281</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9157,23 +9193,23 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>74</v>
@@ -9185,11 +9221,11 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>154</v>
+        <v>87</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9216,13 +9252,11 @@
         <v>74</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -9240,7 +9274,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9260,21 +9294,23 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E79" s="2"/>
+      <c r="E79" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>74</v>
@@ -9286,11 +9322,11 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>157</v>
+        <v>86</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9341,7 +9377,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9361,21 +9397,23 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E80" s="2"/>
+      <c r="E80" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>74</v>
@@ -9387,11 +9425,11 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9442,7 +9480,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9462,17 +9500,17 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="F81" t="s" s="2">
         <v>80</v>
@@ -9490,11 +9528,11 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9545,7 +9583,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9565,17 +9603,17 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F82" t="s" s="2">
         <v>80</v>
@@ -9593,11 +9631,11 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" t="s" s="2">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9648,13 +9686,13 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>74</v>
@@ -9668,23 +9706,23 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>74</v>
@@ -9696,11 +9734,11 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>175</v>
+        <v>103</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9751,13 +9789,13 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>74</v>
@@ -9771,10 +9809,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9785,7 +9823,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>74</v>
@@ -9797,10 +9835,12 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>285</v>
+        <v>158</v>
       </c>
       <c r="L84" s="2"/>
-      <c r="M84" s="2"/>
+      <c r="M84" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -9850,13 +9890,13 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>286</v>
+        <v>160</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>74</v>
@@ -9870,10 +9910,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9884,7 +9924,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>74</v>
@@ -9896,10 +9936,12 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>288</v>
+        <v>103</v>
       </c>
       <c r="L85" s="2"/>
-      <c r="M85" s="2"/>
+      <c r="M85" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -9949,13 +9991,13 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>289</v>
+        <v>163</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>74</v>
@@ -9978,7 +10020,9 @@
       <c r="D86" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E86" s="2"/>
+      <c r="E86" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="F86" t="s" s="2">
         <v>80</v>
       </c>
@@ -9995,10 +10039,12 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>291</v>
+        <v>166</v>
       </c>
       <c r="L86" s="2"/>
-      <c r="M86" s="2"/>
+      <c r="M86" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10048,7 +10094,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>292</v>
+        <v>168</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10068,21 +10114,23 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E87" s="2"/>
+      <c r="E87" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>74</v>
@@ -10094,10 +10142,12 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>294</v>
+        <v>171</v>
       </c>
       <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
+      <c r="M87" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -10147,13 +10197,13 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>295</v>
+        <v>173</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>74</v>
@@ -10167,21 +10217,23 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E88" s="2"/>
+      <c r="E88" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>74</v>
@@ -10193,10 +10245,12 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>297</v>
+        <v>176</v>
       </c>
       <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
+      <c r="M88" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -10246,13 +10300,13 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>298</v>
+        <v>179</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>74</v>
@@ -10266,10 +10320,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10277,10 +10331,10 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>74</v>
@@ -10292,7 +10346,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>96</v>
+        <v>294</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10345,21 +10399,516 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L90" s="2"/>
+      <c r="M90" s="2"/>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K91" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AG89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK89" t="s" s="2">
+      <c r="L91" s="2"/>
+      <c r="M91" s="2"/>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L92" s="2"/>
+      <c r="M92" s="2"/>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L93" s="2"/>
+      <c r="M93" s="2"/>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2"/>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK94" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2992" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="316">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -857,6 +857,9 @@
     <t>ServiceEvent.performer.assignedEntity.id</t>
   </si>
   <si>
+    <t>Identifiant du responsable</t>
+  </si>
+  <si>
     <t>AssignedEntity.id</t>
   </si>
   <si>
@@ -885,7 +888,9 @@
     <t>ServiceEvent.performer.assignedEntity.id.extension</t>
   </si>
   <si>
-    <t>Valeur de l’identifiant</t>
+    <t>Valeur de l’identifiant.
+- Pour le PS, valeur de PS_IdNat (voir CI-SIS_ANX_SOURCES-DONNEES-PERSONNES-STRUCTURES).
+- Pour le patient/usager, valeur de l'INS du patient/usager.</t>
   </si>
   <si>
     <t>ServiceEvent.performer.assignedEntity.sdtcIdentifiedBy</t>
@@ -901,6 +906,9 @@
     <t>ServiceEvent.performer.assignedEntity.code</t>
   </si>
   <si>
+    <t>Profession ou rôle du responsable</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
   </si>
   <si>
@@ -947,6 +955,9 @@
 </t>
   </si>
   <si>
+    <t>Adresse géopostale</t>
+  </si>
+  <si>
     <t>AssignedEntity.addr</t>
   </si>
   <si>
@@ -957,6 +968,9 @@
 </t>
   </si>
   <si>
+    <t>Coordonnées télécom</t>
+  </si>
+  <si>
     <t>AssignedEntity.telecom</t>
   </si>
   <si>
@@ -967,6 +981,13 @@
 </t>
   </si>
   <si>
+    <t>Personne physique : 
+- Obligatoire pour un professionnel 
+- Obligatoire pour un patient/usager 
+- Non utilisé pour un SNR 
+- Non utilisé pour le DP</t>
+  </si>
+  <si>
     <t>AssignedEntity.assignedPerson</t>
   </si>
   <si>
@@ -975,6 +996,11 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-organization}
 </t>
+  </si>
+  <si>
+    <t>Structure de rattachement :
+- Pour un PS : Organisation pour le compte de laquelle intervient le PS.
+- Pour un patient : seul l'élément standardIndustryClassCode est renseigné (cas particulier des documents d'expression personnelle du patient).</t>
   </si>
   <si>
     <t>AssignedEntity.representedOrganization</t>
@@ -8409,7 +8435,9 @@
       <c r="K70" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="L70" s="2"/>
+      <c r="L70" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8460,7 +8488,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -8480,10 +8508,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8581,10 +8609,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8684,10 +8712,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8787,10 +8815,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8818,10 +8846,10 @@
         <v>113</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -8892,10 +8920,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8923,7 +8951,7 @@
         <v>103</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>119</v>
@@ -8997,10 +9025,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9023,7 +9051,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9076,7 +9104,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9096,10 +9124,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9124,7 +9152,9 @@
       <c r="K77" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L77" s="2"/>
+      <c r="L77" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9155,7 +9185,7 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>74</v>
@@ -9173,7 +9203,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9193,10 +9223,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9294,10 +9324,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9397,10 +9427,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9500,10 +9530,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9603,10 +9633,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9706,10 +9736,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9809,10 +9839,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9910,10 +9940,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10011,10 +10041,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10114,10 +10144,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10217,10 +10247,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10320,10 +10350,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10346,9 +10376,11 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="L89" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10399,7 +10431,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10419,10 +10451,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10445,9 +10477,11 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="L90" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10498,7 +10532,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10518,10 +10552,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10544,9 +10578,11 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="L91" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10597,7 +10633,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10617,10 +10653,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10643,9 +10679,11 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="L92" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -10696,7 +10734,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10716,10 +10754,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10742,7 +10780,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10795,7 +10833,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10815,10 +10853,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10894,7 +10932,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ServiceEvent représente un évènement (acte, traitement, diagnostic, etc…) décrit dans le document. 
+    <t>L'élément de l'en-tête du CDA serviceEvent permet de représenter un évènement (acte, traitement, diagnostic, etc…) décrit dans le document. 
 L'occurrence de documentationOf/serviceEvent contenant les données de l’évènement documenté principal doit inclure un élément effectiveTime et un élément performer renseignés, sans recours à l'attribut nullFlavor.</t>
   </si>
   <si>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
